--- a/admin/templates/[試験名]_受験結果_([氏名])_[yyyymmdd].xlsx
+++ b/admin/templates/[試験名]_受験結果_([氏名])_[yyyymmdd].xlsx
@@ -262,11 +262,11 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
